--- a/DUS/DUS_YCOA_Mapping_Review_V4.xlsx
+++ b/DUS/DUS_YCOA_Mapping_Review_V4.xlsx
@@ -40538,4 +40538,10 @@
     <oddFooter>&amp;C&amp;8 &amp;A – Seite &amp;P von &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
+</clbl:labelList>
 </file>